--- a/Decks/Piratas.xlsx
+++ b/Decks/Piratas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755639DF-2E68-407B-B39D-3EC3D476A3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D829163A-CF00-4282-A09A-F8FDEB837781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF92CB1A-8BB6-4359-963F-39B958AE9BAA}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>Reliquary Tower</t>
   </si>
   <si>
-    <t>Mines of Moria</t>
-  </si>
-  <si>
     <t>Archway of Innovation</t>
   </si>
   <si>
@@ -363,6 +360,9 @@
   </si>
   <si>
     <t>Blood Crypt</t>
+  </si>
+  <si>
+    <t>Return the Favor</t>
   </si>
 </sst>
 </file>
@@ -803,7 +803,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B67" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -894,10 +894,10 @@
       </c>
       <c r="B9" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1047,10 +1047,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1122,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1137,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1152,10 +1152,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1167,10 +1167,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1182,10 +1182,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1272,10 +1272,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1287,10 +1287,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1302,10 +1302,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1317,10 +1317,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1332,30 +1332,33 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B39" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>26</v>
+        <v>33</v>
+      </c>
+      <c r="E39" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1373,7 +1376,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1385,13 +1388,10 @@
       <c r="D41" t="s">
         <v>35</v>
       </c>
-      <c r="E41" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B42" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B43" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B45" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1526,37 +1526,38 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D52" t="s">
-        <v>47</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F52"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1572,7 +1573,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1588,7 +1589,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1604,7 +1605,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1620,7 +1621,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1636,7 +1637,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1652,7 +1653,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1668,30 +1669,30 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F60"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D61" t="s">
         <v>58</v>
@@ -1700,7 +1701,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1716,38 +1717,38 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B63" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C63&lt;&gt;D63</f>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="D63" t="s">
-        <v>60</v>
-      </c>
-      <c r="F63"/>
+        <v>88</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B64" s="5" t="b">
-        <f>C64&lt;&gt;D64</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="D64" t="s">
-        <v>89</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F64"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1763,7 +1764,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1779,26 +1780,26 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B67" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D67" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F67"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B68" s="5" t="b">
-        <f t="shared" ref="B68:B101" si="1">C68&lt;&gt;D68</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
@@ -1811,7 +1812,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1827,7 +1828,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1843,23 +1844,23 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D71" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F71"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1875,30 +1876,30 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>71</v>
       </c>
       <c r="D73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F73"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D74" t="s">
         <v>73</v>
@@ -1907,7 +1908,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1923,7 +1924,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1939,7 +1940,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1955,7 +1956,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1971,23 +1972,22 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D79" t="s">
-        <v>78</v>
-      </c>
-      <c r="F79"/>
+        <v>79</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2017,22 +2017,22 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D82" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2047,7 +2047,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D86" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2107,7 +2107,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2122,7 +2122,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2152,168 +2152,168 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D91" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D92" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B93" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C93&lt;&gt;D93</f>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D93" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B94" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="D94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D98" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F98"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D99" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D101" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Piratas.xlsx
+++ b/Decks/Piratas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D829163A-CF00-4282-A09A-F8FDEB837781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE71C6F-FCC7-4F84-8778-B4C68D6B30F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF92CB1A-8BB6-4359-963F-39B958AE9BAA}"/>
   </bookViews>
@@ -206,9 +206,6 @@
     <t>Warkite Marauder</t>
   </si>
   <si>
-    <t>Dire Fleet Poisoner</t>
-  </si>
-  <si>
     <t>Broadside Bombardiers</t>
   </si>
   <si>
@@ -320,9 +317,6 @@
     <t>Revel in Riches</t>
   </si>
   <si>
-    <t>Torment of Hailfire</t>
-  </si>
-  <si>
     <t>Prancha</t>
   </si>
   <si>
@@ -363,6 +357,12 @@
   </si>
   <si>
     <t>Return the Favor</t>
+  </si>
+  <si>
+    <t>Frostcliff Siege</t>
+  </si>
+  <si>
+    <t>Hawkeye's Bow</t>
   </si>
 </sst>
 </file>
@@ -879,10 +879,10 @@
       </c>
       <c r="B8" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1325,17 +1325,17 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B38" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1353,7 +1353,7 @@
         <v>33</v>
       </c>
       <c r="E39" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1371,7 +1371,7 @@
         <v>34</v>
       </c>
       <c r="E40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1676,10 +1676,10 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" t="s">
         <v>56</v>
-      </c>
-      <c r="D60" t="s">
-        <v>57</v>
       </c>
       <c r="F60"/>
     </row>
@@ -1692,10 +1692,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D61" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F61"/>
     </row>
@@ -1708,10 +1708,10 @@
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F62"/>
     </row>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D63" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F64"/>
     </row>
@@ -1755,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D65" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F65"/>
     </row>
@@ -1771,549 +1771,549 @@
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D66" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F66"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F67"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D68" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F68"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F69"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D70" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F70"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>67</v>
+      </c>
+      <c r="B71" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B71" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="D71" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F71"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D72" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F72"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>71</v>
       </c>
       <c r="D73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F73"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D74" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F74"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D75" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F75"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D76" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F76"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D77" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D78" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F78"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="D79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D81" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="D82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D86" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D88" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D89" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D91" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D92" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B93" s="5" t="b">
         <f>C93&lt;&gt;D93</f>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D93" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D94" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>93</v>
+      </c>
+      <c r="B95" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B95" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="D95" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D96" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D97" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D98" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F98"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D99" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D100" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D101" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Piratas.xlsx
+++ b/Decks/Piratas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE71C6F-FCC7-4F84-8778-B4C68D6B30F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D779189B-2F5A-4A3A-9D13-5A476EC6ED8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF92CB1A-8BB6-4359-963F-39B958AE9BAA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="112">
   <si>
     <t>Função</t>
   </si>
@@ -248,9 +248,6 @@
     <t>Ramirez DePietro, Pillager</t>
   </si>
   <si>
-    <t>Wyll's Reversal</t>
-  </si>
-  <si>
     <t>Glint-Horn Buccaneer</t>
   </si>
   <si>
@@ -363,6 +360,18 @@
   </si>
   <si>
     <t>Hawkeye's Bow</t>
+  </si>
+  <si>
+    <t>Smaug the Magnificent</t>
+  </si>
+  <si>
+    <t>Smaug, Wicked Worm</t>
+  </si>
+  <si>
+    <t>Orcrist, Goblin-Cleaver</t>
+  </si>
+  <si>
+    <t>Glasspool Mimic</t>
   </si>
 </sst>
 </file>
@@ -803,7 +812,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B65" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1032,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1332,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1353,7 +1362,7 @@
         <v>33</v>
       </c>
       <c r="E39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1371,7 +1380,7 @@
         <v>34</v>
       </c>
       <c r="E40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1440,13 +1449,13 @@
       </c>
       <c r="B45" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D45" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1676,7 +1685,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D60" t="s">
         <v>56</v>
@@ -1724,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -1755,26 +1764,26 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D65" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="F65"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B66" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D66" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F66"/>
     </row>
@@ -1783,14 +1792,14 @@
         <v>62</v>
       </c>
       <c r="B67" s="5" t="b">
-        <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D67" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F67"/>
     </row>
@@ -1803,10 +1812,10 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D68" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F68"/>
     </row>
@@ -1819,26 +1828,26 @@
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D69" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F69"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D70" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F70"/>
     </row>
@@ -1851,10 +1860,10 @@
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D71" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F71"/>
     </row>
@@ -1867,10 +1876,10 @@
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D72" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F72"/>
     </row>
@@ -1956,23 +1965,22 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D78" t="s">
-        <v>76</v>
-      </c>
-      <c r="F78"/>
+        <v>77</v>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1987,7 +1995,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2000,24 +2008,24 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>80</v>
-      </c>
-      <c r="D81" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>81</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2030,9 +2038,9 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2045,9 +2053,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2060,24 +2068,24 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D85" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>85</v>
-      </c>
-      <c r="D85" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>86</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2090,234 +2098,236 @@
         <v>88</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B87" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C87&lt;&gt;D87</f>
+        <v>1</v>
       </c>
       <c r="C87" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D87" t="s">
+        <v>110</v>
+      </c>
+      <c r="F87"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>85</v>
+      </c>
+      <c r="B88" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D88" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>86</v>
-      </c>
-      <c r="B88" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C88" s="4" t="s">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>85</v>
+      </c>
+      <c r="B89" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D89" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>86</v>
-      </c>
-      <c r="B89" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C89" s="4" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>85</v>
+      </c>
+      <c r="B90" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D89" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>86</v>
-      </c>
-      <c r="B90" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C90" s="4" t="s">
+      <c r="D90" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>85</v>
+      </c>
+      <c r="B91" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D91" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>85</v>
+      </c>
+      <c r="B92" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D92" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>92</v>
-      </c>
-      <c r="D90" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>86</v>
-      </c>
-      <c r="B91" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D91" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>86</v>
-      </c>
-      <c r="B92" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D92" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>93</v>
       </c>
       <c r="B93" s="5" t="b">
         <f>C93&lt;&gt;D93</f>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D93" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B94" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C94" s="4" t="s">
+      <c r="D94" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>92</v>
+      </c>
+      <c r="B95" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D95" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>93</v>
-      </c>
-      <c r="B95" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C95" s="4" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>92</v>
+      </c>
+      <c r="B96" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D96" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>93</v>
-      </c>
-      <c r="B96" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D96" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D97" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D98" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F98"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D99" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D100" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D101" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
